--- a/artfynd/A 33066-2026 artfynd.xlsx
+++ b/artfynd/A 33066-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,57 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123409668</v>
+        <v>137481363</v>
       </c>
       <c r="B2" t="n">
-        <v>92348</v>
+        <v>81504</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5420</v>
+        <v>1049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vikingaborgen, Vikingaborgen, Srm</t>
+          <t>Körunda, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>665223</v>
+        <v>665141</v>
       </c>
       <c r="R2" t="n">
-        <v>6545779</v>
+        <v>6545687</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,17 +740,27 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Ösmo</t>
+          <t>Sorunda</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,27 +775,27 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Nim Rautiainen Byström</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Nim Rautiainen Byström</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123409668</t>
+          <t>https://artportalen.se/Sighting/137481363</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>92163303</v>
+        <v>137481368</v>
       </c>
       <c r="B3" t="n">
-        <v>91930</v>
+        <v>92185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,40 +803,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nynäshamn, Srm</t>
+          <t>Körunda, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>665002</v>
+        <v>665100</v>
       </c>
       <c r="R3" t="n">
-        <v>6545724</v>
+        <v>6545773</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -859,12 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-11-26</t>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-11-26</t>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -873,75 +881,71 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sven Bengtsson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sven Bengtsson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/92163303</t>
+          <t>https://artportalen.se/Sighting/137481368</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>92163301</v>
+        <v>137481365</v>
       </c>
       <c r="B4" t="n">
-        <v>91872</v>
+        <v>91189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>1962</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nynäshamn, Srm</t>
+          <t>Körunda, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>665107</v>
+        <v>665129</v>
       </c>
       <c r="R4" t="n">
-        <v>6545826</v>
+        <v>6545700</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -965,12 +969,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-11-26</t>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-11-26</t>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,75 +993,80 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sven Bengtsson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sven Bengtsson</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/92163301</t>
+          <t>https://artportalen.se/Sighting/137481365</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>92163302</v>
+        <v>123409668</v>
       </c>
       <c r="B5" t="n">
-        <v>79327</v>
+        <v>92348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5420</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nynäshamn, Srm</t>
+          <t>Vikingaborgen, Vikingaborgen, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>665147</v>
+        <v>665223</v>
       </c>
       <c r="R5" t="n">
-        <v>6545920</v>
+        <v>6545779</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1066,17 +1085,17 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Sorunda</t>
+          <t>Ösmo</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-11-26</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-11-26</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1085,80 +1104,74 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sven Bengtsson</t>
+          <t>Nim Rautiainen Byström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sven Bengtsson</t>
+          <t>Nim Rautiainen Byström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/92163302</t>
+          <t>https://artportalen.se/Sighting/123409668</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123408933</v>
+        <v>92163303</v>
       </c>
       <c r="B6" t="n">
-        <v>57141</v>
+        <v>91930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Vikingaborgen, Vikingaborgen, Srm</t>
+          <t>Nynäshamn, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>665127</v>
+        <v>665002</v>
       </c>
       <c r="R6" t="n">
-        <v>6545778</v>
+        <v>6545724</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1182,12 +1195,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2020-11-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2020-11-26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1196,79 +1209,72 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Nim Rautiainen Byström</t>
+          <t>Sven Bengtsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Nim Rautiainen Byström</t>
+          <t>Sven Bengtsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123408933</t>
+          <t>https://artportalen.se/Sighting/92163303</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123409591</v>
+        <v>137481366</v>
       </c>
       <c r="B7" t="n">
-        <v>57141</v>
+        <v>92206</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vikingaborgen, Vikingaborgen, Srm</t>
+          <t>Körunda, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>665217</v>
+        <v>665138</v>
       </c>
       <c r="R7" t="n">
-        <v>6545784</v>
+        <v>6545708</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1287,17 +1293,27 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Ösmo</t>
+          <t>Sorunda</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,18 +1328,1575 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Nim Rautiainen Byström</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Nim Rautiainen Byström</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137481366</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>92163301</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Nynäshamn, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>665107</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6545826</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sorunda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2020-11-26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2020-11-26</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Sven Bengtsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Sven Bengtsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92163301</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137481376</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92148</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Körunda, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>665122</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6545809</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sorunda</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137481376</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>137481364</v>
+      </c>
+      <c r="B10" t="n">
+        <v>93523</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Körunda, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>665126</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6545686</v>
+      </c>
+      <c r="S10" t="n">
+        <v>17</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sorunda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137481364</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137481367</v>
+      </c>
+      <c r="B11" t="n">
+        <v>93523</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Körunda, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>665133</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6545722</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sorunda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137481367</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137481371</v>
+      </c>
+      <c r="B12" t="n">
+        <v>93523</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Körunda, Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>665030</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6545787</v>
+      </c>
+      <c r="S12" t="n">
+        <v>8</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sorunda</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137481371</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137481374</v>
+      </c>
+      <c r="B13" t="n">
+        <v>93523</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Körunda, Srm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>665130</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6545776</v>
+      </c>
+      <c r="S13" t="n">
+        <v>6</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sorunda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137481374</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>92163302</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Nynäshamn, Srm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>665147</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6545920</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Sorunda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2020-11-26</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2020-11-26</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Sven Bengtsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Sven Bengtsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92163302</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137481362</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80154</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Körunda, Srm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>665156</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6545677</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Sorunda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137481362</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>137481370</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80154</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Körunda, Srm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>665005</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6545754</v>
+      </c>
+      <c r="S16" t="n">
+        <v>21</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Sorunda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137481370</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>137481372</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80154</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Körunda, Srm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>665036</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6545793</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Sorunda</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137481372</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>137481377</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80154</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Körunda, Srm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>665178</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6545822</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Sorunda</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137481377</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>123408933</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Vikingaborgen, Vikingaborgen, Srm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>665127</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6545778</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Sorunda</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Nim Rautiainen Byström</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Nim Rautiainen Byström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123408933</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>123409591</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Vikingaborgen, Vikingaborgen, Srm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>665217</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6545784</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ösmo</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Nim Rautiainen Byström</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Nim Rautiainen Byström</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/123409591</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>137481373</v>
+      </c>
+      <c r="B21" t="n">
+        <v>5188</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Körunda, Srm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>665084</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6545793</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Sorunda</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Gnagspår</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137481373</t>
         </is>
       </c>
     </row>
@@ -1335,6 +2908,20 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33066-2026 artfynd.xlsx
+++ b/artfynd/A 33066-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137481363</v>
       </c>
       <c r="B2" t="n">
-        <v>81504</v>
+        <v>81508</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137481368</v>
       </c>
       <c r="B3" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137481365</v>
       </c>
       <c r="B4" t="n">
-        <v>91189</v>
+        <v>91193</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>137481366</v>
       </c>
       <c r="B7" t="n">
-        <v>92206</v>
+        <v>92210</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>137481376</v>
       </c>
       <c r="B9" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>137481364</v>
       </c>
       <c r="B10" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>137481367</v>
       </c>
       <c r="B11" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>137481371</v>
       </c>
       <c r="B12" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         <v>137481374</v>
       </c>
       <c r="B13" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>137481362</v>
       </c>
       <c r="B15" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>137481370</v>
       </c>
       <c r="B16" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>137481372</v>
       </c>
       <c r="B17" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2456,7 +2456,7 @@
         <v>137481377</v>
       </c>
       <c r="B18" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
